--- a/extenbooks/S508.xlsx
+++ b/extenbooks/S508.xlsx
@@ -601,7 +601,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B52"/>
+  <dimension ref="A1:B55"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -700,7 +700,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>1929–2025</t>
+          <t>1948-1961</t>
         </is>
       </c>
     </row>
@@ -722,7 +722,11 @@
           <t>Figures</t>
         </is>
       </c>
-      <c r="B10" t="inlineStr"/>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>Fig_5_8</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -762,54 +766,55 @@
     </row>
     <row r="14"/>
     <row r="15">
-      <c r="A15" t="inlineStr">
+      <c r="A15" s="4" t="inlineStr">
+        <is>
+          <t>Subseries</t>
+        </is>
+      </c>
+      <c r="B15" s="4" t="inlineStr">
+        <is>
+          <t>source / role</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>S508-A</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>S&amp;T 1994</t>
+        </is>
+      </c>
+    </row>
+    <row r="17"/>
+    <row r="18">
+      <c r="A18" t="inlineStr">
         <is>
           <t>DPR (markdown)</t>
         </is>
       </c>
-      <c r="B15" t="inlineStr"/>
-    </row>
-    <row r="16">
-      <c r="A16" t="inlineStr"/>
-      <c r="B16" t="inlineStr">
-        <is>
-          <t># S508 — Productive Consumption (CON*)</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" t="inlineStr"/>
-      <c r="B17" t="inlineStr"/>
-    </row>
-    <row r="18">
-      <c r="A18" t="inlineStr"/>
-      <c r="B18" t="inlineStr">
-        <is>
-          <t>**Chapter**: 5 — The Marxian Categories</t>
-        </is>
-      </c>
+      <c r="B18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr"/>
       <c r="B19" t="inlineStr">
         <is>
-          <t>**Source Table**: Appendix E.2 (Revenue Accounts), p. 310</t>
+          <t># S508 — Productive Consumption (CON*)</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr"/>
-      <c r="B20" t="inlineStr">
-        <is>
-          <t>**Units**: billions current $</t>
-        </is>
-      </c>
+      <c r="B20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr"/>
       <c r="B21" t="inlineStr">
         <is>
-          <t>**Period**: 1948-1961 (book-period partial; later years require digitization of E.2 second half not in salvaged KB)</t>
+          <t>**Chapter**: 5 — The Marxian Categories</t>
         </is>
       </c>
     </row>
@@ -817,7 +822,7 @@
       <c r="A22" t="inlineStr"/>
       <c r="B22" t="inlineStr">
         <is>
-          <t>**Content Type**: time_series</t>
+          <t>**Source Table**: Appendix E.2 (Revenue Accounts), p. 310</t>
         </is>
       </c>
     </row>
@@ -825,127 +830,127 @@
       <c r="A23" t="inlineStr"/>
       <c r="B23" t="inlineStr">
         <is>
-          <t>**Status**: book_period_partial_1948_1961</t>
+          <t>**Units**: billions current $</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr"/>
-      <c r="B24" t="inlineStr"/>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>**Period**: 1948-1961 (book-period partial; later years require digitization of E.2 second half not in salvaged KB)</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr"/>
       <c r="B25" t="inlineStr">
         <is>
-          <t>## Definition</t>
+          <t>**Content Type**: time_series</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr"/>
-      <c r="B26" t="inlineStr"/>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>**Status**: book_period_partial_1948_1961</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr"/>
-      <c r="B27" t="inlineStr">
-        <is>
-          <t>Productive Consumption (CON*) is total household consumption attributable to productive activities under the book's Marxian classification. Distinguished from total CON by excluding the unproductive (trade/finance/government services) share.</t>
-        </is>
-      </c>
+      <c r="B27" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr"/>
-      <c r="B28" t="inlineStr"/>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>## Definition</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr"/>
-      <c r="B29" t="inlineStr">
-        <is>
-          <t>## Source</t>
-        </is>
-      </c>
+      <c r="B29" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr"/>
-      <c r="B30" t="inlineStr"/>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>Productive Consumption (CON*) is total household consumption attributable to productive activities under the book's Marxian classification. Distinguished from total CON by excluding the unproductive (trade/finance/government services) share.</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr"/>
-      <c r="B31" t="inlineStr">
-        <is>
-          <t>`data/source/book_tables/TableE2_RevenueAccounts_1948_1961.csv`, column `CON_star`. Loader: `L01_S508_productive_consumption.py` — direct column projection. Processor `P02_S508` is a pass-through.</t>
-        </is>
-      </c>
+      <c r="B31" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr"/>
-      <c r="B32" t="inlineStr"/>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>## Source</t>
+        </is>
+      </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr"/>
-      <c r="B33" t="inlineStr">
-        <is>
-          <t>## Reference</t>
-        </is>
-      </c>
+      <c r="B33" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr"/>
-      <c r="B34" t="inlineStr"/>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>`data/source/book_tables/TableE2_RevenueAccounts_1948_1961.csv`, column `CON_star`. Loader: `L01_S508_productive_consumption.py` — direct column projection. Processor `P02_S508` is a pass-through.</t>
+        </is>
+      </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr"/>
-      <c r="B35" t="inlineStr">
-        <is>
-          <t>Validation benchmark from `validation_config.json` T508: 1948 = 158.46. PASS verified.</t>
-        </is>
-      </c>
+      <c r="B35" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr"/>
-      <c r="B36" t="inlineStr"/>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>## Reference</t>
+        </is>
+      </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr"/>
-      <c r="B37" t="inlineStr">
-        <is>
-          <t>## Provenance</t>
-        </is>
-      </c>
+      <c r="B37" t="inlineStr"/>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr"/>
-      <c r="B38" t="inlineStr"/>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>Validation benchmark from `validation_config.json` T508: 1948 = 158.46. PASS verified.</t>
+        </is>
+      </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr"/>
-      <c r="B39" t="inlineStr">
-        <is>
-          <t>```</t>
-        </is>
-      </c>
+      <c r="B39" t="inlineStr"/>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr"/>
       <c r="B40" t="inlineStr">
         <is>
-          <t>TableE2_RevenueAccounts_1948_1961.csv (col CON_star)</t>
+          <t>## Provenance</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr"/>
-      <c r="B41" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  -&gt; L01_S508 -&gt; data/intermediate/S508.csv</t>
-        </is>
-      </c>
+      <c r="B41" t="inlineStr"/>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr"/>
       <c r="B42" t="inlineStr">
         <is>
-          <t xml:space="preserve">  -&gt; P02_S508 -&gt; data/final/S508.csv</t>
+          <t>```</t>
         </is>
       </c>
     </row>
@@ -953,7 +958,7 @@
       <c r="A43" t="inlineStr"/>
       <c r="B43" t="inlineStr">
         <is>
-          <t xml:space="preserve">  -&gt; V03_S508 -&gt; data/intermediate/validation/S508.json (PASS)</t>
+          <t>TableE2_RevenueAccounts_1948_1961.csv (col CON_star)</t>
         </is>
       </c>
     </row>
@@ -961,53 +966,77 @@
       <c r="A44" t="inlineStr"/>
       <c r="B44" t="inlineStr">
         <is>
-          <t>```</t>
+          <t xml:space="preserve">  -&gt; L01_S508 -&gt; data/intermediate/S508.csv</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr"/>
-      <c r="B45" t="inlineStr"/>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  -&gt; P02_S508 -&gt; data/final/S508.csv</t>
+        </is>
+      </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr"/>
       <c r="B46" t="inlineStr">
         <is>
-          <t>## Coverage Caveat</t>
+          <t xml:space="preserve">  -&gt; V03_S508 -&gt; data/intermediate/validation/S508.json (PASS)</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr"/>
-      <c r="B47" t="inlineStr"/>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>```</t>
+        </is>
+      </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr"/>
-      <c r="B48" t="inlineStr">
-        <is>
-          <t>14-year coverage (1948-1961) is limited by what was digitized in the salvaged KB. To extend through 1989 we would need either (a) digitization of E.2's full appendix (pages 310+ of the book, not yet in the salvaged tables/), or (b) reconstruction from NIPA Table 2.4 plus the productive-sector concordance the book defines in Appendix C. Neither is yet provisioned. Status reflects this honestly rather than fabricating values.</t>
-        </is>
-      </c>
+      <c r="B48" t="inlineStr"/>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr"/>
-      <c r="B49" t="inlineStr"/>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>## Coverage Caveat</t>
+        </is>
+      </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr"/>
-      <c r="B50" t="inlineStr">
-        <is>
-          <t>---</t>
-        </is>
-      </c>
+      <c r="B50" t="inlineStr"/>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr"/>
-      <c r="B51" t="inlineStr"/>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>14-year coverage (1948-1961) is limited by what was digitized in the salvaged KB. To extend through 1989 we would need either (a) digitization of E.2's full appendix (pages 310+ of the book, not yet in the salvaged tables/), or (b) reconstruction from NIPA Table 2.4 plus the productive-sector concordance the book defines in Appendix C. Neither is yet provisioned. Status reflects this honestly rather than fabricating values.</t>
+        </is>
+      </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr"/>
-      <c r="B52" t="inlineStr">
+      <c r="B52" t="inlineStr"/>
+    </row>
+    <row r="53">
+      <c r="A53" t="inlineStr"/>
+      <c r="B53" t="inlineStr">
+        <is>
+          <t>---</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="inlineStr"/>
+      <c r="B54" t="inlineStr"/>
+    </row>
+    <row r="55">
+      <c r="A55" t="inlineStr"/>
+      <c r="B55" t="inlineStr">
         <is>
           <t>*Generated by anu-ingestion (re-authored from scratch).*</t>
         </is>
@@ -1024,10 +1053,10 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C21"/>
+  <dimension ref="A1:C32"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="25" customWidth="1" min="1" max="1"/>
+    <col width="29" customWidth="1" min="1" max="1"/>
     <col width="62" customWidth="1" min="2" max="2"/>
     <col width="62" customWidth="1" min="3" max="3"/>
   </cols>
@@ -1052,184 +1081,317 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>methodology_description</t>
+          <t>verbatim_quote</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>CON* = CON - GVA_ir - RY_con + HH_con - ROW_con. Productive consumption strips out unproductive components from total personal consumption expenditure: imputed rental of owner-occupied housing (GVA_ir), royalties in consumption (RY_con), then adds back household consumption adjustments (HH_con) and removes rest-of-world consumption (ROW_con).</t>
+          <t>CON* = {CON} - GVAir - RYcon - {HHcon} - ROWcon</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>ST_1994, Ch5; Knowledge_Base/equations/page_310_equations.txt</t>
+          <t>ST_1994, Ch5 Sec 5.2, p.95; chunk_12</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>data_source</t>
+          <t>verbatim_quote</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>NIPA sources: Table 1.1.5 line 2 provides total PCE (personal consumption expenditure). Table 6.1 line 73 provides imputed rental value. Additional adjustments from Tables 7.9 and 4.1 for ROW and household sectors. Book data in Table E.2.</t>
+          <t>For all of these reasons, one cannot simply use NIPA data to fill in observations between IO benchmark years. Instead, we use NIPA data directly for components such as GVAp or CON (containing the latest available revisions) and indirectly to interpolate between benchmark estimates of other components such as M'p or RYcon.</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Knowledge_Base/tables/page_310_table_E2.csv; NIPA Tables 1.1.5, 6.1</t>
+          <t>ST_1994, Ch5 Sec 5.2, p.94; chunk_12</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>figure_context</t>
+          <t>verbatim_quote</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>CON* appears in Table E.2 as part of the revenue account but has no dedicated figure. It feeds into the demand-side decomposition of total product.</t>
+          <t>For royalties RY we use the receiving industry's GVA (i.e. GVAry) as the numeraire, as in xi == (RYi/GVAry)IO. This is done because some royalties such as RYi and RYx-im appear as components of highly unstable final-demand totals like I or X-IM (see Figure 5.1). Benchmark coefficients created by dividing these royalties by unstable totals are not very useful.</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>ST_1994, Table E.2</t>
+          <t>ST_1994, Ch5 Sec 5.2, p.96; chunk_12</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>component_detail</t>
+          <t>verbatim_quote</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>GVA_ir (imputed rental) is subtracted because owner-occupied housing is classified as a FIRE activity and is therefore unproductive. RY_con (royalties) represents rents on natural resources embedded in consumption. The HH and ROW adjustments reconcile domestic productive consumption with NIPA reporting conventions.</t>
+          <t>CON* = {CON} − GVAir − RYcon − {HHcon} − ROWcon.</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>ST_1994, Ch5; Knowledge_Base/tables/page_340_variables_definitions.csv</t>
+          <t>ST_1994</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>caveat</t>
+          <t>verbatim_quote</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>NIPA line numbers have shifted across benchmark revisions. The specific line references (1.1.5 line 2, 6.1 line 73) must be verified against the current NIPA vintage. Historical concordance is needed for extension.</t>
+          <t>Take from NIPA directly: {CON, IG, X-IM, G, WG}. Interpolate between benchmarks: M's, RYs, and ROWs.</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>CHAPTER_5_INVESTIGATION.md</t>
-        </is>
-      </c>
-    </row>
-    <row r="7"/>
+          <t>ST_1994</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>verbatim_quote</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>CON*IO/CON*NIPA: 1.04 → 0.99 (convergence). Totals fairly close. Individual components (investment, net exports) differ substantially. Stability of ratios: Indicates same trends in both data sets.</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>ST_1994</t>
+        </is>
+      </c>
+    </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>methodology_summary</t>
+          <t>methodology_description</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Productive consumption adjusts total PCE by removing imputed rent, royalties, and ROW components. Formula: CON* = CON - GVA_ir - RY_con + HH_con - ROW_con. NIPA Tables 1.1.5 and 6.1 are primary sources.</t>
-        </is>
-      </c>
-    </row>
-    <row r="9"/>
+          <t>CON* = CON - GVA_ir - RY_con + HH_con - ROW_con. Productive consumption strips out unproductive components from total personal consumption expenditure: imputed rental of owner-occupied housing (GVA_ir), royalties in consumption (RY_con), then adds back household consumption adjustments (HH_con) and removes rest-of-world consumption (ROW_con).</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>ST_1994, Ch5; Knowledge_Base/equations/page_310_equations.txt</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>data_source</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>NIPA sources: Table 1.1.5 line 2 provides total PCE (personal consumption expenditure). Table 6.1 line 73 provides imputed rental value. Additional adjustments from Tables 7.9 and 4.1 for ROW and household sectors. Book data in Table E.2.</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>Knowledge_Base/tables/page_310_table_E2.csv; NIPA Tables 1.1.5, 6.1</t>
+        </is>
+      </c>
+    </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>known_issues:</t>
+          <t>figure_context</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>CON* appears in Table E.2 as part of the revenue account but has no dedicated figure. It feeds into the demand-side decomposition of total product.</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>ST_1994, Table E.2</t>
         </is>
       </c>
     </row>
     <row r="11">
-      <c r="A11" t="inlineStr"/>
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>component_detail</t>
+        </is>
+      </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>NIPA line numbers may shift across vintages</t>
+          <t>GVA_ir (imputed rental) is subtracted because owner-occupied housing is classified as a FIRE activity and is therefore unproductive. RY_con (royalties) represents rents on natural resources embedded in consumption. The HH and ROW adjustments reconcile domestic productive consumption with NIPA reporting conventions.</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>ST_1994, Ch5; Knowledge_Base/tables/page_340_variables_definitions.csv</t>
         </is>
       </c>
     </row>
     <row r="12">
-      <c r="A12" t="inlineStr"/>
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>caveat</t>
+        </is>
+      </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Owner-occupied housing imputation methodology has changed over time</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" t="inlineStr"/>
-      <c r="B13" t="inlineStr">
-        <is>
-          <t>No dedicated figure in the book</t>
-        </is>
-      </c>
-    </row>
-    <row r="14"/>
+          <t>NIPA line numbers have shifted across benchmark revisions. The specific line references (1.1.5 line 2, 6.1 line 73) must be verified against the current NIPA vintage. Historical concordance is needed for extension.</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>CHAPTER_5_INVESTIGATION.md</t>
+        </is>
+      </c>
+    </row>
+    <row r="13"/>
+    <row r="14">
+      <c r="A14" s="4" t="inlineStr">
+        <is>
+          <t>VERBATIM QUOTES (top-level)</t>
+        </is>
+      </c>
+      <c r="B14" s="4" t="inlineStr"/>
+      <c r="C14" s="4" t="inlineStr"/>
+    </row>
     <row r="15">
-      <c r="A15" t="inlineStr">
-        <is>
-          <t>cross_references:</t>
-        </is>
+      <c r="A15" t="inlineStr"/>
+      <c r="B15" t="inlineStr"/>
+      <c r="C15" t="n">
+        <v>95</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr"/>
-      <c r="B16" t="inlineStr">
-        <is>
-          <t>S501</t>
-        </is>
+      <c r="B16" t="inlineStr"/>
+      <c r="C16" t="n">
+        <v>95</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr"/>
-      <c r="B17" t="inlineStr">
-        <is>
-          <t>S509</t>
-        </is>
+      <c r="B17" t="inlineStr"/>
+      <c r="C17" t="n">
+        <v>98</v>
       </c>
     </row>
     <row r="18"/>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>citations:</t>
-        </is>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" t="inlineStr">
-        <is>
-          <t>ST_1994</t>
-        </is>
-      </c>
-      <c r="B20" t="inlineStr">
-        <is>
-          <t>Shaikh, Anwar, and E. Ahmet Tonak. 1994. Measuring the Wealth of Nations: The Political Economy of National Accounts. Cambridge University Press.</t>
-        </is>
-      </c>
-    </row>
+          <t>methodology_summary</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>Productive consumption adjusts total PCE by removing imputed rent, royalties, and ROW components. Formula: CON* = CON - GVA_ir - RY_con + HH_con - ROW_con. NIPA Tables 1.1.5 and 6.1 are primary sources.</t>
+        </is>
+      </c>
+    </row>
+    <row r="20"/>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
+          <t>known_issues:</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr"/>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>NIPA line numbers may shift across vintages</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr"/>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>Owner-occupied housing imputation methodology has changed over time</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr"/>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>No dedicated figure in the book</t>
+        </is>
+      </c>
+    </row>
+    <row r="25"/>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>cross_references:</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr"/>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>S501</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr"/>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>S509</t>
+        </is>
+      </c>
+    </row>
+    <row r="29"/>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>citations:</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>ST_1994</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>Shaikh, Anwar, and E. Ahmet Tonak. 1994. Measuring the Wealth of Nations: The Political Economy of National Accounts. Cambridge University Press.</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
           <t>BEA_NIPA</t>
         </is>
       </c>
-      <c r="B21" t="inlineStr">
+      <c r="B32" t="inlineStr">
         <is>
           <t>Bureau of Economic Analysis. National Income and Product Accounts. https://apps.bea.gov/iTable/</t>
         </is>
@@ -1246,7 +1408,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E9"/>
+  <dimension ref="A1:E12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -1309,7 +1471,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>null — series does not extend beyond book period</t>
+          <t>null - series does not extend beyond book period</t>
         </is>
       </c>
     </row>
@@ -1330,7 +1492,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>{}</t>
+          <t>{"1948": 158.46}</t>
         </is>
       </c>
     </row>
@@ -1354,7 +1516,43 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>level_series</t>
+          <t>dollar_series</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>tolerance_class</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>dollar_series</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>tolerance_rel</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>0.01</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>tolerance_abs</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>1.0</t>
         </is>
       </c>
     </row>

--- a/extenbooks/S508.xlsx
+++ b/extenbooks/S508.xlsx
@@ -447,7 +447,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B16"/>
+  <dimension ref="A1:B44"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="38" customWidth="1" min="1" max="1"/>
@@ -588,6 +588,230 @@
       </c>
       <c r="B16" s="3" t="n">
         <v>286.69</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="n">
+        <v>1962</v>
+      </c>
+      <c r="B17" s="3" t="n">
+        <v>303.64</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="n">
+        <v>1963</v>
+      </c>
+      <c r="B18" s="3" t="n">
+        <v>319.67</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="n">
+        <v>1964</v>
+      </c>
+      <c r="B19" s="3" t="n">
+        <v>343.59</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="n">
+        <v>1965</v>
+      </c>
+      <c r="B20" s="3" t="n">
+        <v>370.24</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="n">
+        <v>1966</v>
+      </c>
+      <c r="B21" s="3" t="n">
+        <v>400.85</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="n">
+        <v>1967</v>
+      </c>
+      <c r="B22" s="3" t="n">
+        <v>421.33</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="n">
+        <v>1968</v>
+      </c>
+      <c r="B23" s="3" t="n">
+        <v>464.47</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="n">
+        <v>1969</v>
+      </c>
+      <c r="B24" s="3" t="n">
+        <v>502.02</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="n">
+        <v>1970</v>
+      </c>
+      <c r="B25" s="3" t="n">
+        <v>537.49</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="n">
+        <v>1971</v>
+      </c>
+      <c r="B26" s="3" t="n">
+        <v>580.5700000000001</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="n">
+        <v>1972</v>
+      </c>
+      <c r="B27" s="3" t="n">
+        <v>637.77</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="n">
+        <v>1973</v>
+      </c>
+      <c r="B28" s="3" t="n">
+        <v>708.0700000000001</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="n">
+        <v>1974</v>
+      </c>
+      <c r="B29" s="3" t="n">
+        <v>776.7</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="n">
+        <v>1975</v>
+      </c>
+      <c r="B30" s="3" t="n">
+        <v>860.42</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="n">
+        <v>1976</v>
+      </c>
+      <c r="B31" s="3" t="n">
+        <v>961.28</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="n">
+        <v>1977</v>
+      </c>
+      <c r="B32" s="3" t="n">
+        <v>1068.01</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="n">
+        <v>1978</v>
+      </c>
+      <c r="B33" s="3" t="n">
+        <v>1185.13</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="n">
+        <v>1979</v>
+      </c>
+      <c r="B34" s="3" t="n">
+        <v>1321.81</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="n">
+        <v>1980</v>
+      </c>
+      <c r="B35" s="3" t="n">
+        <v>1454.98</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="n">
+        <v>1981</v>
+      </c>
+      <c r="B36" s="3" t="n">
+        <v>1599.86</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="n">
+        <v>1982</v>
+      </c>
+      <c r="B37" s="3" t="n">
+        <v>1710.89</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="n">
+        <v>1983</v>
+      </c>
+      <c r="B38" s="3" t="n">
+        <v>1853.81</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="n">
+        <v>1984</v>
+      </c>
+      <c r="B39" s="3" t="n">
+        <v>2013.39</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="n">
+        <v>1985</v>
+      </c>
+      <c r="B40" s="3" t="n">
+        <v>2161.53</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="n">
+        <v>1986</v>
+      </c>
+      <c r="B41" s="3" t="n">
+        <v>2275.73</v>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="n">
+        <v>1987</v>
+      </c>
+      <c r="B42" s="3" t="n">
+        <v>2434.73</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="n">
+        <v>1988</v>
+      </c>
+      <c r="B43" s="3" t="n">
+        <v>2619.76</v>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="n">
+        <v>1989</v>
+      </c>
+      <c r="B44" s="3" t="n">
+        <v>2777.29</v>
       </c>
     </row>
   </sheetData>
@@ -601,7 +825,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B55"/>
+  <dimension ref="A1:B57"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -700,7 +924,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>1948-1961</t>
+          <t>1948-1989</t>
         </is>
       </c>
     </row>
@@ -712,7 +936,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>book_period_partial_1948_1961</t>
+          <t>book_period_validated</t>
         </is>
       </c>
     </row>
@@ -854,7 +1078,7 @@
       <c r="A26" t="inlineStr"/>
       <c r="B26" t="inlineStr">
         <is>
-          <t>**Status**: book_period_partial_1948_1961</t>
+          <t>**Status**: book_period_validated</t>
         </is>
       </c>
     </row>
@@ -866,7 +1090,7 @@
       <c r="A28" t="inlineStr"/>
       <c r="B28" t="inlineStr">
         <is>
-          <t>## Definition</t>
+          <t>&gt; **v1.3 note:** Status widened from `book_period_partial_1948_1961` to `book_period_validated`. The panel-backed rebuild (B6) supplies real book-arm data across the full book period 1948-1989 (previously partial 1948-1961); V03 PASS post-rebuild.</t>
         </is>
       </c>
     </row>
@@ -878,7 +1102,7 @@
       <c r="A30" t="inlineStr"/>
       <c r="B30" t="inlineStr">
         <is>
-          <t>Productive Consumption (CON*) is total household consumption attributable to productive activities under the book's Marxian classification. Distinguished from total CON by excluding the unproductive (trade/finance/government services) share.</t>
+          <t>## Definition</t>
         </is>
       </c>
     </row>
@@ -890,7 +1114,7 @@
       <c r="A32" t="inlineStr"/>
       <c r="B32" t="inlineStr">
         <is>
-          <t>## Source</t>
+          <t>Productive Consumption (CON*) is total household consumption attributable to productive activities under the book's Marxian classification. Distinguished from total CON by excluding the unproductive (trade/finance/government services) share.</t>
         </is>
       </c>
     </row>
@@ -902,7 +1126,7 @@
       <c r="A34" t="inlineStr"/>
       <c r="B34" t="inlineStr">
         <is>
-          <t>`data/source/book_tables/TableE2_RevenueAccounts_1948_1961.csv`, column `CON_star`. Loader: `L01_S508_productive_consumption.py` — direct column projection. Processor `P02_S508` is a pass-through.</t>
+          <t>## Source</t>
         </is>
       </c>
     </row>
@@ -914,7 +1138,7 @@
       <c r="A36" t="inlineStr"/>
       <c r="B36" t="inlineStr">
         <is>
-          <t>## Reference</t>
+          <t>`data/source/book_tables/TableE2_RevenueAccounts_1948_1961.csv`, column `CON_star`. Loader: `L01_S508_productive_consumption.py` — direct column projection. Processor `P02_S508` is a pass-through.</t>
         </is>
       </c>
     </row>
@@ -926,7 +1150,7 @@
       <c r="A38" t="inlineStr"/>
       <c r="B38" t="inlineStr">
         <is>
-          <t>Validation benchmark from `validation_config.json` T508: 1948 = 158.46. PASS verified.</t>
+          <t>## Reference</t>
         </is>
       </c>
     </row>
@@ -938,7 +1162,7 @@
       <c r="A40" t="inlineStr"/>
       <c r="B40" t="inlineStr">
         <is>
-          <t>## Provenance</t>
+          <t>Validation benchmark from `validation_config.json` T508: 1948 = 158.46. PASS verified.</t>
         </is>
       </c>
     </row>
@@ -950,23 +1174,19 @@
       <c r="A42" t="inlineStr"/>
       <c r="B42" t="inlineStr">
         <is>
-          <t>```</t>
+          <t>## Provenance</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr"/>
-      <c r="B43" t="inlineStr">
-        <is>
-          <t>TableE2_RevenueAccounts_1948_1961.csv (col CON_star)</t>
-        </is>
-      </c>
+      <c r="B43" t="inlineStr"/>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr"/>
       <c r="B44" t="inlineStr">
         <is>
-          <t xml:space="preserve">  -&gt; L01_S508 -&gt; data/intermediate/S508.csv</t>
+          <t>```</t>
         </is>
       </c>
     </row>
@@ -974,7 +1194,7 @@
       <c r="A45" t="inlineStr"/>
       <c r="B45" t="inlineStr">
         <is>
-          <t xml:space="preserve">  -&gt; P02_S508 -&gt; data/final/S508.csv</t>
+          <t>TableE2_RevenueAccounts_1948_1961.csv (col CON_star)</t>
         </is>
       </c>
     </row>
@@ -982,7 +1202,7 @@
       <c r="A46" t="inlineStr"/>
       <c r="B46" t="inlineStr">
         <is>
-          <t xml:space="preserve">  -&gt; V03_S508 -&gt; data/intermediate/validation/S508.json (PASS)</t>
+          <t xml:space="preserve">  -&gt; L01_S508 -&gt; data/intermediate/S508.csv</t>
         </is>
       </c>
     </row>
@@ -990,19 +1210,23 @@
       <c r="A47" t="inlineStr"/>
       <c r="B47" t="inlineStr">
         <is>
-          <t>```</t>
+          <t xml:space="preserve">  -&gt; P02_S508 -&gt; data/final/S508.csv</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr"/>
-      <c r="B48" t="inlineStr"/>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  -&gt; V03_S508 -&gt; data/intermediate/validation/S508.json (PASS)</t>
+        </is>
+      </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr"/>
       <c r="B49" t="inlineStr">
         <is>
-          <t>## Coverage Caveat</t>
+          <t>```</t>
         </is>
       </c>
     </row>
@@ -1014,7 +1238,7 @@
       <c r="A51" t="inlineStr"/>
       <c r="B51" t="inlineStr">
         <is>
-          <t>14-year coverage (1948-1961) is limited by what was digitized in the salvaged KB. To extend through 1989 we would need either (a) digitization of E.2's full appendix (pages 310+ of the book, not yet in the salvaged tables/), or (b) reconstruction from NIPA Table 2.4 plus the productive-sector concordance the book defines in Appendix C. Neither is yet provisioned. Status reflects this honestly rather than fabricating values.</t>
+          <t>## Coverage Caveat</t>
         </is>
       </c>
     </row>
@@ -1026,7 +1250,7 @@
       <c r="A53" t="inlineStr"/>
       <c r="B53" t="inlineStr">
         <is>
-          <t>---</t>
+          <t>14-year coverage (1948-1961) is limited by what was digitized in the salvaged KB. To extend through 1989 we would need either (a) digitization of E.2's full appendix (pages 310+ of the book, not yet in the salvaged tables/), or (b) reconstruction from NIPA Table 2.4 plus the productive-sector concordance the book defines in Appendix C. Neither is yet provisioned. Status reflects this honestly rather than fabricating values.</t>
         </is>
       </c>
     </row>
@@ -1037,6 +1261,18 @@
     <row r="55">
       <c r="A55" t="inlineStr"/>
       <c r="B55" t="inlineStr">
+        <is>
+          <t>---</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="inlineStr"/>
+      <c r="B56" t="inlineStr"/>
+    </row>
+    <row r="57">
+      <c r="A57" t="inlineStr"/>
+      <c r="B57" t="inlineStr">
         <is>
           <t>*Generated by anu-ingestion (re-authored from scratch).*</t>
         </is>

--- a/extenbooks/S508.xlsx
+++ b/extenbooks/S508.xlsx
@@ -972,7 +972,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>P01</t>
+          <t>P02</t>
         </is>
       </c>
     </row>
@@ -1728,7 +1728,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>{"1948": 158.46}</t>
+          <t>{"1948": 158.46, "1989": 2777.29}</t>
         </is>
       </c>
     </row>
